--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799510</v>
+        <v>122799506</v>
       </c>
       <c r="B2" t="n">
-        <v>90924</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312300</v>
+        <v>312417</v>
       </c>
       <c r="R2" t="n">
-        <v>6524200</v>
+        <v>6524342</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799505</v>
+        <v>122799498</v>
       </c>
       <c r="B3" t="n">
-        <v>92221</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312414</v>
+        <v>312152</v>
       </c>
       <c r="R3" t="n">
-        <v>6524576</v>
+        <v>6524347</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +878,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799507</v>
+        <v>122799509</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>90997</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312377</v>
+        <v>312384</v>
       </c>
       <c r="R4" t="n">
-        <v>6524277</v>
+        <v>6524233</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,22 +993,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799504</v>
+        <v>122799500</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>95943</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1039,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312390</v>
+        <v>312356</v>
       </c>
       <c r="R5" t="n">
-        <v>6524571</v>
+        <v>6524442</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,21 +1113,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799512</v>
+        <v>122799504</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,14 +1165,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312193</v>
+        <v>312390</v>
       </c>
       <c r="R6" t="n">
-        <v>6524137</v>
+        <v>6524571</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,17 +1184,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1245,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799501</v>
+        <v>122799502</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>92225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,7 +1289,7 @@
         <v>312331</v>
       </c>
       <c r="R7" t="n">
-        <v>6524539</v>
+        <v>6524544</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,21 +1332,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1362,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799513</v>
+        <v>122799512</v>
       </c>
       <c r="B8" t="n">
-        <v>96880</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,38 +1360,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312162</v>
+        <v>312193</v>
       </c>
       <c r="R8" t="n">
-        <v>6524162</v>
+        <v>6524137</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,17 +1403,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1448,6 +1434,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1464,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799496</v>
+        <v>122799507</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,43 +1477,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312061</v>
+        <v>312377</v>
       </c>
       <c r="R9" t="n">
-        <v>6524311</v>
+        <v>6524277</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,17 +1554,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1586,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799506</v>
+        <v>122799499</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>92225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,25 +1594,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312417</v>
+        <v>312153</v>
       </c>
       <c r="R10" t="n">
-        <v>6524342</v>
+        <v>6524315</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,21 +1668,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1703,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799509</v>
+        <v>122799505</v>
       </c>
       <c r="B11" t="n">
-        <v>90993</v>
+        <v>92225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1700,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5321</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312384</v>
+        <v>312414</v>
       </c>
       <c r="R11" t="n">
-        <v>6524233</v>
+        <v>6524576</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1787,24 +1768,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1821,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799500</v>
+        <v>122799503</v>
       </c>
       <c r="B12" t="n">
-        <v>95935</v>
+        <v>92225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312356</v>
+        <v>312342</v>
       </c>
       <c r="R12" t="n">
-        <v>6524442</v>
+        <v>6524559</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1923,10 +1888,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799499</v>
+        <v>122799496</v>
       </c>
       <c r="B13" t="n">
-        <v>92221</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,34 +1904,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312153</v>
+        <v>312061</v>
       </c>
       <c r="R13" t="n">
-        <v>6524315</v>
+        <v>6524311</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,6 +1979,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2025,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799497</v>
+        <v>122799515</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>92225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,39 +2026,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312066</v>
+        <v>312041</v>
       </c>
       <c r="R14" t="n">
-        <v>6524348</v>
+        <v>6524041</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2085,17 +2065,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2116,21 +2096,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2147,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799503</v>
+        <v>122799508</v>
       </c>
       <c r="B15" t="n">
-        <v>92221</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,25 +2124,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2187,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312342</v>
+        <v>312401</v>
       </c>
       <c r="R15" t="n">
-        <v>6524559</v>
+        <v>6524257</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,6 +2198,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2249,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799515</v>
+        <v>122799501</v>
       </c>
       <c r="B16" t="n">
-        <v>92221</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,38 +2241,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312041</v>
+        <v>312331</v>
       </c>
       <c r="R16" t="n">
-        <v>6524041</v>
+        <v>6524539</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2304,17 +2284,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2335,6 +2315,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2351,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799498</v>
+        <v>122799511</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>95943</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,38 +2358,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312152</v>
+        <v>312263</v>
       </c>
       <c r="R17" t="n">
-        <v>6524347</v>
+        <v>6524163</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2406,17 +2401,17 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2440,17 +2435,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799508</v>
+        <v>122799497</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>5173</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,38 +2475,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312401</v>
+        <v>312066</v>
       </c>
       <c r="R18" t="n">
-        <v>6524257</v>
+        <v>6524348</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2557,17 +2557,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799502</v>
+        <v>122799510</v>
       </c>
       <c r="B19" t="n">
-        <v>92221</v>
+        <v>90928</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,21 +2601,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312331</v>
+        <v>312300</v>
       </c>
       <c r="R19" t="n">
-        <v>6524544</v>
+        <v>6524200</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2671,6 +2671,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2687,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799511</v>
+        <v>122799513</v>
       </c>
       <c r="B20" t="n">
-        <v>95935</v>
+        <v>96888</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,34 +2718,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312263</v>
+        <v>312162</v>
       </c>
       <c r="R20" t="n">
-        <v>6524163</v>
+        <v>6524162</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,17 +2757,17 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2773,21 +2788,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799500</v>
+        <v>122799504</v>
       </c>
       <c r="B5" t="n">
-        <v>95943</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,25 +1039,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312356</v>
+        <v>312390</v>
       </c>
       <c r="R5" t="n">
-        <v>6524442</v>
+        <v>6524571</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,6 +1113,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1129,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799504</v>
+        <v>122799500</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>95943</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312390</v>
+        <v>312356</v>
       </c>
       <c r="R6" t="n">
-        <v>6524571</v>
+        <v>6524442</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,21 +1230,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799501</v>
+        <v>122799511</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>95943</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,38 +2241,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312331</v>
+        <v>312263</v>
       </c>
       <c r="R16" t="n">
-        <v>6524539</v>
+        <v>6524163</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2284,17 +2284,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799511</v>
+        <v>122799501</v>
       </c>
       <c r="B17" t="n">
-        <v>95943</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,38 +2358,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312263</v>
+        <v>312331</v>
       </c>
       <c r="R17" t="n">
-        <v>6524163</v>
+        <v>6524539</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2401,17 +2401,17 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799506</v>
+        <v>122799502</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312417</v>
+        <v>312331</v>
       </c>
       <c r="R2" t="n">
-        <v>6524342</v>
+        <v>6524544</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799498</v>
+        <v>122799508</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312152</v>
+        <v>312401</v>
       </c>
       <c r="R3" t="n">
-        <v>6524347</v>
+        <v>6524257</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,17 +866,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799509</v>
+        <v>122799504</v>
       </c>
       <c r="B4" t="n">
-        <v>90997</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312384</v>
+        <v>312390</v>
       </c>
       <c r="R4" t="n">
-        <v>6524233</v>
+        <v>6524571</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,23 +978,22 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1027,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799504</v>
+        <v>122799496</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312390</v>
+        <v>312061</v>
       </c>
       <c r="R5" t="n">
-        <v>6524571</v>
+        <v>6524311</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,17 +1105,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1144,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799500</v>
+        <v>122799498</v>
       </c>
       <c r="B6" t="n">
-        <v>95943</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312356</v>
+        <v>312152</v>
       </c>
       <c r="R6" t="n">
-        <v>6524442</v>
+        <v>6524347</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,6 +1219,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1246,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799502</v>
+        <v>122799500</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>95943</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312331</v>
+        <v>312356</v>
       </c>
       <c r="R7" t="n">
-        <v>6524544</v>
+        <v>6524442</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799512</v>
+        <v>122799511</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>95943</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312193</v>
+        <v>312263</v>
       </c>
       <c r="R8" t="n">
-        <v>6524137</v>
+        <v>6524163</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799507</v>
+        <v>122799510</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90928</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312377</v>
+        <v>312300</v>
       </c>
       <c r="R9" t="n">
-        <v>6524277</v>
+        <v>6524200</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,17 +1558,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1582,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799499</v>
+        <v>122799507</v>
       </c>
       <c r="B10" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,25 +1598,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312153</v>
+        <v>312377</v>
       </c>
       <c r="R10" t="n">
-        <v>6524315</v>
+        <v>6524277</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1668,6 +1672,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1684,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799505</v>
+        <v>122799513</v>
       </c>
       <c r="B11" t="n">
-        <v>92225</v>
+        <v>96888</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1724,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312414</v>
+        <v>312162</v>
       </c>
       <c r="R11" t="n">
-        <v>6524576</v>
+        <v>6524162</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1786,7 +1805,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799503</v>
+        <v>122799515</v>
       </c>
       <c r="B12" t="n">
         <v>92225</v>
@@ -1822,14 +1841,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312342</v>
+        <v>312041</v>
       </c>
       <c r="R12" t="n">
-        <v>6524559</v>
+        <v>6524041</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,17 +1860,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1888,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799496</v>
+        <v>122799509</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>90997</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,39 +1923,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>5321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312061</v>
+        <v>312384</v>
       </c>
       <c r="R13" t="n">
-        <v>6524311</v>
+        <v>6524233</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,22 +1991,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2010,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799515</v>
+        <v>122799497</v>
       </c>
       <c r="B14" t="n">
-        <v>92225</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,34 +2041,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312041</v>
+        <v>312066</v>
       </c>
       <c r="R14" t="n">
-        <v>6524041</v>
+        <v>6524348</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2065,17 +2085,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2096,6 +2116,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2112,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799508</v>
+        <v>122799505</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,25 +2159,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312401</v>
+        <v>312414</v>
       </c>
       <c r="R15" t="n">
-        <v>6524257</v>
+        <v>6524576</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2198,21 +2233,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2229,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799511</v>
+        <v>122799512</v>
       </c>
       <c r="B16" t="n">
-        <v>95943</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,25 +2261,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312263</v>
+        <v>312193</v>
       </c>
       <c r="R16" t="n">
-        <v>6524163</v>
+        <v>6524137</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2346,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799501</v>
+        <v>122799503</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,25 +2378,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2386,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312331</v>
+        <v>312342</v>
       </c>
       <c r="R17" t="n">
-        <v>6524539</v>
+        <v>6524559</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,21 +2452,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2463,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799497</v>
+        <v>122799499</v>
       </c>
       <c r="B18" t="n">
-        <v>5173</v>
+        <v>92225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,39 +2484,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312066</v>
+        <v>312153</v>
       </c>
       <c r="R18" t="n">
-        <v>6524348</v>
+        <v>6524315</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,21 +2554,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2585,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799510</v>
+        <v>122799501</v>
       </c>
       <c r="B19" t="n">
-        <v>90928</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2597,25 +2582,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312300</v>
+        <v>312331</v>
       </c>
       <c r="R19" t="n">
-        <v>6524200</v>
+        <v>6524539</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2674,17 +2659,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2702,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799513</v>
+        <v>122799506</v>
       </c>
       <c r="B20" t="n">
-        <v>96888</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,25 +2699,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312162</v>
+        <v>312417</v>
       </c>
       <c r="R20" t="n">
-        <v>6524162</v>
+        <v>6524342</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,6 +2773,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799502</v>
+        <v>122799513</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>96890</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312331</v>
+        <v>312162</v>
       </c>
       <c r="R2" t="n">
-        <v>6524544</v>
+        <v>6524162</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799508</v>
+        <v>122799496</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312401</v>
+        <v>312061</v>
       </c>
       <c r="R3" t="n">
-        <v>6524257</v>
+        <v>6524311</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,17 +871,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799504</v>
+        <v>122799505</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312390</v>
+        <v>312414</v>
       </c>
       <c r="R4" t="n">
-        <v>6524571</v>
+        <v>6524576</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,21 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799496</v>
+        <v>122799512</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1013,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312061</v>
+        <v>312193</v>
       </c>
       <c r="R5" t="n">
-        <v>6524311</v>
+        <v>6524137</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,17 +1056,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1105,17 +1090,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1133,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799498</v>
+        <v>122799506</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1173,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312152</v>
+        <v>312417</v>
       </c>
       <c r="R6" t="n">
-        <v>6524347</v>
+        <v>6524342</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,17 +1207,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1250,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799500</v>
+        <v>122799507</v>
       </c>
       <c r="B7" t="n">
-        <v>95943</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312356</v>
+        <v>312377</v>
       </c>
       <c r="R7" t="n">
-        <v>6524442</v>
+        <v>6524277</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,6 +1321,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799511</v>
+        <v>122799509</v>
       </c>
       <c r="B8" t="n">
-        <v>95943</v>
+        <v>90997</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1368,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312263</v>
+        <v>312384</v>
       </c>
       <c r="R8" t="n">
-        <v>6524163</v>
+        <v>6524233</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1407,17 +1407,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1436,22 +1436,23 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799510</v>
+        <v>122799502</v>
       </c>
       <c r="B9" t="n">
-        <v>90928</v>
+        <v>92225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312300</v>
+        <v>312331</v>
       </c>
       <c r="R9" t="n">
-        <v>6524200</v>
+        <v>6524544</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,21 +1556,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1586,7 +1572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799507</v>
+        <v>122799504</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1626,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312377</v>
+        <v>312390</v>
       </c>
       <c r="R10" t="n">
-        <v>6524277</v>
+        <v>6524571</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1703,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799513</v>
+        <v>122799503</v>
       </c>
       <c r="B11" t="n">
-        <v>96888</v>
+        <v>92225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312162</v>
+        <v>312342</v>
       </c>
       <c r="R11" t="n">
-        <v>6524162</v>
+        <v>6524559</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1805,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799515</v>
+        <v>122799511</v>
       </c>
       <c r="B12" t="n">
-        <v>92225</v>
+        <v>95945</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1807,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1831,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312041</v>
+        <v>312263</v>
       </c>
       <c r="R12" t="n">
-        <v>6524041</v>
+        <v>6524163</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1891,6 +1877,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1907,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799509</v>
+        <v>122799497</v>
       </c>
       <c r="B13" t="n">
-        <v>90997</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,34 +1924,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5321</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312384</v>
+        <v>312066</v>
       </c>
       <c r="R13" t="n">
-        <v>6524233</v>
+        <v>6524348</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1991,23 +1997,22 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2025,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799497</v>
+        <v>122799508</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,43 +2042,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312066</v>
+        <v>312401</v>
       </c>
       <c r="R14" t="n">
-        <v>6524348</v>
+        <v>6524257</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2119,17 +2119,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799505</v>
+        <v>122799500</v>
       </c>
       <c r="B15" t="n">
-        <v>92225</v>
+        <v>95945</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,21 +2163,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312414</v>
+        <v>312356</v>
       </c>
       <c r="R15" t="n">
-        <v>6524576</v>
+        <v>6524442</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799512</v>
+        <v>122799515</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,25 +2261,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312193</v>
+        <v>312041</v>
       </c>
       <c r="R16" t="n">
-        <v>6524137</v>
+        <v>6524041</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,21 +2335,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2366,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799503</v>
+        <v>122799510</v>
       </c>
       <c r="B17" t="n">
-        <v>92225</v>
+        <v>90928</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,21 +2367,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312342</v>
+        <v>312300</v>
       </c>
       <c r="R17" t="n">
-        <v>6524559</v>
+        <v>6524200</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,6 +2437,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799506</v>
+        <v>122799498</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312417</v>
+        <v>312152</v>
       </c>
       <c r="R20" t="n">
-        <v>6524342</v>
+        <v>6524347</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799513</v>
+        <v>122799502</v>
       </c>
       <c r="B2" t="n">
-        <v>96890</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312162</v>
+        <v>312331</v>
       </c>
       <c r="R2" t="n">
-        <v>6524162</v>
+        <v>6524544</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799496</v>
+        <v>122799510</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>90928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312061</v>
+        <v>312300</v>
       </c>
       <c r="R3" t="n">
-        <v>6524311</v>
+        <v>6524200</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,17 +866,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799505</v>
+        <v>122799506</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312414</v>
+        <v>312417</v>
       </c>
       <c r="R4" t="n">
-        <v>6524576</v>
+        <v>6524342</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,6 +980,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799512</v>
+        <v>122799501</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1037,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312193</v>
+        <v>312331</v>
       </c>
       <c r="R5" t="n">
-        <v>6524137</v>
+        <v>6524539</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,17 +1066,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1118,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799506</v>
+        <v>122799497</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312417</v>
+        <v>312066</v>
       </c>
       <c r="R6" t="n">
-        <v>6524342</v>
+        <v>6524348</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,17 +1222,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799507</v>
+        <v>122799503</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312377</v>
+        <v>312342</v>
       </c>
       <c r="R7" t="n">
-        <v>6524277</v>
+        <v>6524559</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,21 +1336,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799509</v>
+        <v>122799507</v>
       </c>
       <c r="B8" t="n">
-        <v>90997</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312384</v>
+        <v>312377</v>
       </c>
       <c r="R8" t="n">
-        <v>6524233</v>
+        <v>6524277</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,23 +1436,22 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1470,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799502</v>
+        <v>122799496</v>
       </c>
       <c r="B9" t="n">
-        <v>92225</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312331</v>
+        <v>312061</v>
       </c>
       <c r="R9" t="n">
-        <v>6524544</v>
+        <v>6524311</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1556,6 +1560,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1572,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799504</v>
+        <v>122799499</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,25 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312390</v>
+        <v>312153</v>
       </c>
       <c r="R10" t="n">
-        <v>6524571</v>
+        <v>6524315</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,21 +1677,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1689,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799503</v>
+        <v>122799500</v>
       </c>
       <c r="B11" t="n">
-        <v>92225</v>
+        <v>95945</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312342</v>
+        <v>312356</v>
       </c>
       <c r="R11" t="n">
-        <v>6524559</v>
+        <v>6524442</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799511</v>
+        <v>122799513</v>
       </c>
       <c r="B12" t="n">
-        <v>95945</v>
+        <v>96890</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,34 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312263</v>
+        <v>312162</v>
       </c>
       <c r="R12" t="n">
-        <v>6524163</v>
+        <v>6524162</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,17 +1850,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1877,21 +1881,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1908,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799497</v>
+        <v>122799512</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,43 +1909,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312066</v>
+        <v>312193</v>
       </c>
       <c r="R13" t="n">
-        <v>6524348</v>
+        <v>6524137</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,17 +1952,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2002,17 +1986,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2030,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799508</v>
+        <v>122799509</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90997</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,25 +2026,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2070,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312401</v>
+        <v>312384</v>
       </c>
       <c r="R14" t="n">
-        <v>6524257</v>
+        <v>6524233</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,22 +2098,23 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2147,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799500</v>
+        <v>122799504</v>
       </c>
       <c r="B15" t="n">
-        <v>95945</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,25 +2144,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2187,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312356</v>
+        <v>312390</v>
       </c>
       <c r="R15" t="n">
-        <v>6524442</v>
+        <v>6524571</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,6 +2218,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2351,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799510</v>
+        <v>122799498</v>
       </c>
       <c r="B17" t="n">
-        <v>90928</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312300</v>
+        <v>312152</v>
       </c>
       <c r="R17" t="n">
-        <v>6524200</v>
+        <v>6524347</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2440,17 +2440,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799499</v>
+        <v>122799511</v>
       </c>
       <c r="B18" t="n">
-        <v>92225</v>
+        <v>95945</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,34 +2484,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312153</v>
+        <v>312263</v>
       </c>
       <c r="R18" t="n">
-        <v>6524315</v>
+        <v>6524163</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,17 +2523,17 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2554,6 +2554,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2570,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799501</v>
+        <v>122799505</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,25 +2597,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312331</v>
+        <v>312414</v>
       </c>
       <c r="R19" t="n">
-        <v>6524539</v>
+        <v>6524576</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2656,21 +2671,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799498</v>
+        <v>122799508</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312152</v>
+        <v>312401</v>
       </c>
       <c r="R20" t="n">
-        <v>6524347</v>
+        <v>6524257</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799502</v>
+        <v>122799510</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>90928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312331</v>
+        <v>312300</v>
       </c>
       <c r="R2" t="n">
-        <v>6524544</v>
+        <v>6524200</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799510</v>
+        <v>122799502</v>
       </c>
       <c r="B3" t="n">
-        <v>90928</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312300</v>
+        <v>312331</v>
       </c>
       <c r="R3" t="n">
-        <v>6524200</v>
+        <v>6524544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,21 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799503</v>
+        <v>122799507</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312342</v>
+        <v>312377</v>
       </c>
       <c r="R7" t="n">
-        <v>6524559</v>
+        <v>6524277</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,6 +1336,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799507</v>
+        <v>122799503</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312377</v>
+        <v>312342</v>
       </c>
       <c r="R8" t="n">
-        <v>6524277</v>
+        <v>6524559</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,21 +1453,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799510</v>
+        <v>122799502</v>
       </c>
       <c r="B2" t="n">
-        <v>90928</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312300</v>
+        <v>312331</v>
       </c>
       <c r="R2" t="n">
-        <v>6524200</v>
+        <v>6524544</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799502</v>
+        <v>122799510</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>90928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312331</v>
+        <v>312300</v>
       </c>
       <c r="R3" t="n">
-        <v>6524544</v>
+        <v>6524200</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +863,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799507</v>
+        <v>122799503</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312377</v>
+        <v>312342</v>
       </c>
       <c r="R7" t="n">
-        <v>6524277</v>
+        <v>6524559</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,21 +1336,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799503</v>
+        <v>122799507</v>
       </c>
       <c r="B8" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312342</v>
+        <v>312377</v>
       </c>
       <c r="R8" t="n">
-        <v>6524559</v>
+        <v>6524277</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,6 +1438,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799502</v>
+        <v>122799513</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>96898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312331</v>
+        <v>312162</v>
       </c>
       <c r="R2" t="n">
-        <v>6524544</v>
+        <v>6524162</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799510</v>
+        <v>122799498</v>
       </c>
       <c r="B3" t="n">
-        <v>90928</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312300</v>
+        <v>312152</v>
       </c>
       <c r="R3" t="n">
-        <v>6524200</v>
+        <v>6524347</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,17 +866,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799501</v>
+        <v>122799502</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
         <v>312331</v>
       </c>
       <c r="R5" t="n">
-        <v>6524539</v>
+        <v>6524544</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,21 +1097,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799497</v>
+        <v>122799509</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>91005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312066</v>
+        <v>312384</v>
       </c>
       <c r="R6" t="n">
-        <v>6524348</v>
+        <v>6524233</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,22 +1197,23 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1250,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799503</v>
+        <v>122799505</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312342</v>
+        <v>312414</v>
       </c>
       <c r="R7" t="n">
-        <v>6524559</v>
+        <v>6524576</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799507</v>
+        <v>122799497</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,38 +1345,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312377</v>
+        <v>312066</v>
       </c>
       <c r="R8" t="n">
-        <v>6524277</v>
+        <v>6524348</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1441,17 +1427,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1591,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799499</v>
+        <v>122799503</v>
       </c>
       <c r="B10" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312153</v>
+        <v>312342</v>
       </c>
       <c r="R10" t="n">
-        <v>6524315</v>
+        <v>6524559</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799500</v>
+        <v>122799508</v>
       </c>
       <c r="B11" t="n">
-        <v>95945</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1691,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312356</v>
+        <v>312401</v>
       </c>
       <c r="R11" t="n">
-        <v>6524442</v>
+        <v>6524257</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1779,6 +1765,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1795,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799513</v>
+        <v>122799499</v>
       </c>
       <c r="B12" t="n">
-        <v>96890</v>
+        <v>92233</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312162</v>
+        <v>312153</v>
       </c>
       <c r="R12" t="n">
-        <v>6524162</v>
+        <v>6524315</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799512</v>
+        <v>122799510</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90936</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,38 +1910,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312193</v>
+        <v>312300</v>
       </c>
       <c r="R13" t="n">
-        <v>6524137</v>
+        <v>6524200</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,17 +1953,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1986,17 +1987,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2014,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799509</v>
+        <v>122799511</v>
       </c>
       <c r="B14" t="n">
-        <v>90997</v>
+        <v>95953</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,34 +2031,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5321</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312384</v>
+        <v>312263</v>
       </c>
       <c r="R14" t="n">
-        <v>6524233</v>
+        <v>6524163</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2069,17 +2070,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2098,23 +2099,22 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799504</v>
+        <v>122799500</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>95953</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312390</v>
+        <v>312356</v>
       </c>
       <c r="R15" t="n">
-        <v>6524571</v>
+        <v>6524442</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2218,21 +2218,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2252,7 +2237,7 @@
         <v>122799515</v>
       </c>
       <c r="B16" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799498</v>
+        <v>122799507</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2391,10 +2376,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312152</v>
+        <v>312377</v>
       </c>
       <c r="R17" t="n">
-        <v>6524347</v>
+        <v>6524277</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2440,17 +2425,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2468,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799511</v>
+        <v>122799501</v>
       </c>
       <c r="B18" t="n">
-        <v>95945</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,38 +2465,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312263</v>
+        <v>312331</v>
       </c>
       <c r="R18" t="n">
-        <v>6524163</v>
+        <v>6524539</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,17 +2508,17 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2585,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799505</v>
+        <v>122799512</v>
       </c>
       <c r="B19" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2597,38 +2582,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312414</v>
+        <v>312193</v>
       </c>
       <c r="R19" t="n">
-        <v>6524576</v>
+        <v>6524137</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2640,17 +2625,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2671,6 +2656,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799508</v>
+        <v>122799504</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312401</v>
+        <v>312390</v>
       </c>
       <c r="R20" t="n">
-        <v>6524257</v>
+        <v>6524571</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2234,10 +2234,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799515</v>
+        <v>122799507</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,38 +2246,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312041</v>
+        <v>312377</v>
       </c>
       <c r="R16" t="n">
-        <v>6524041</v>
+        <v>6524277</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2289,17 +2289,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2320,6 +2320,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2336,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799507</v>
+        <v>122799515</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,38 +2363,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312377</v>
+        <v>312041</v>
       </c>
       <c r="R17" t="n">
-        <v>6524277</v>
+        <v>6524041</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2391,17 +2406,17 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2422,21 +2437,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799513</v>
+        <v>122799496</v>
       </c>
       <c r="B2" t="n">
-        <v>96898</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312162</v>
+        <v>312061</v>
       </c>
       <c r="R2" t="n">
-        <v>6524162</v>
+        <v>6524311</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799498</v>
+        <v>122799513</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>96898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312152</v>
+        <v>312162</v>
       </c>
       <c r="R3" t="n">
-        <v>6524347</v>
+        <v>6524162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799506</v>
+        <v>122799499</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312417</v>
+        <v>312153</v>
       </c>
       <c r="R4" t="n">
-        <v>6524342</v>
+        <v>6524315</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,21 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799502</v>
+        <v>122799506</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312331</v>
+        <v>312417</v>
       </c>
       <c r="R5" t="n">
-        <v>6524544</v>
+        <v>6524342</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,6 +1087,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799509</v>
+        <v>122799500</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>95953</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312384</v>
+        <v>312356</v>
       </c>
       <c r="R6" t="n">
-        <v>6524233</v>
+        <v>6524442</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,24 +1202,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1231,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799505</v>
+        <v>122799503</v>
       </c>
       <c r="B7" t="n">
         <v>92233</v>
@@ -1271,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312414</v>
+        <v>312342</v>
       </c>
       <c r="R7" t="n">
-        <v>6524576</v>
+        <v>6524559</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1333,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799497</v>
+        <v>122799505</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>92233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,39 +1338,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312066</v>
+        <v>312414</v>
       </c>
       <c r="R8" t="n">
-        <v>6524348</v>
+        <v>6524576</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,21 +1408,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1455,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799496</v>
+        <v>122799497</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312061</v>
+        <v>312066</v>
       </c>
       <c r="R9" t="n">
-        <v>6524311</v>
+        <v>6524348</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1577,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799503</v>
+        <v>122799502</v>
       </c>
       <c r="B10" t="n">
         <v>92233</v>
@@ -1617,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312342</v>
+        <v>312331</v>
       </c>
       <c r="R10" t="n">
-        <v>6524559</v>
+        <v>6524544</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799508</v>
+        <v>122799504</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1719,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312401</v>
+        <v>312390</v>
       </c>
       <c r="R11" t="n">
-        <v>6524257</v>
+        <v>6524571</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1796,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799499</v>
+        <v>122799510</v>
       </c>
       <c r="B12" t="n">
-        <v>92233</v>
+        <v>90936</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312153</v>
+        <v>312300</v>
       </c>
       <c r="R12" t="n">
-        <v>6524315</v>
+        <v>6524200</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,6 +1851,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1898,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799510</v>
+        <v>122799507</v>
       </c>
       <c r="B13" t="n">
-        <v>90936</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,25 +1894,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312300</v>
+        <v>312377</v>
       </c>
       <c r="R13" t="n">
-        <v>6524200</v>
+        <v>6524277</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,17 +1971,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2015,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799511</v>
+        <v>122799501</v>
       </c>
       <c r="B14" t="n">
-        <v>95953</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,38 +2011,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312263</v>
+        <v>312331</v>
       </c>
       <c r="R14" t="n">
-        <v>6524163</v>
+        <v>6524539</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,17 +2054,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2132,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799500</v>
+        <v>122799515</v>
       </c>
       <c r="B15" t="n">
-        <v>95953</v>
+        <v>92233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,34 +2132,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312356</v>
+        <v>312041</v>
       </c>
       <c r="R15" t="n">
-        <v>6524442</v>
+        <v>6524041</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2187,17 +2171,17 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2234,10 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799507</v>
+        <v>122799511</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>95953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,38 +2230,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312377</v>
+        <v>312263</v>
       </c>
       <c r="R16" t="n">
-        <v>6524277</v>
+        <v>6524163</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2289,17 +2273,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2351,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799515</v>
+        <v>122799498</v>
       </c>
       <c r="B17" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,38 +2347,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312041</v>
+        <v>312152</v>
       </c>
       <c r="R17" t="n">
-        <v>6524041</v>
+        <v>6524347</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2406,17 +2390,17 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2437,6 +2421,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2453,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799501</v>
+        <v>122799508</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2493,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312331</v>
+        <v>312401</v>
       </c>
       <c r="R18" t="n">
-        <v>6524539</v>
+        <v>6524257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2570,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799512</v>
+        <v>122799509</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>91005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,38 +2581,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312193</v>
+        <v>312384</v>
       </c>
       <c r="R19" t="n">
-        <v>6524137</v>
+        <v>6524233</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2625,17 +2624,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2654,22 +2653,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799504</v>
+        <v>122799512</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2723,14 +2723,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312390</v>
+        <v>312193</v>
       </c>
       <c r="R20" t="n">
-        <v>6524571</v>
+        <v>6524137</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,17 +2742,17 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799496</v>
+        <v>122799507</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312061</v>
+        <v>312377</v>
       </c>
       <c r="R2" t="n">
-        <v>6524311</v>
+        <v>6524277</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,17 +764,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799513</v>
+        <v>122799500</v>
       </c>
       <c r="B3" t="n">
-        <v>96898</v>
+        <v>95953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312162</v>
+        <v>312356</v>
       </c>
       <c r="R3" t="n">
-        <v>6524162</v>
+        <v>6524442</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799499</v>
+        <v>122799506</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312153</v>
+        <v>312417</v>
       </c>
       <c r="R4" t="n">
-        <v>6524315</v>
+        <v>6524342</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,6 +980,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799506</v>
+        <v>122799499</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312417</v>
+        <v>312153</v>
       </c>
       <c r="R5" t="n">
-        <v>6524342</v>
+        <v>6524315</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,21 +1097,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799500</v>
+        <v>122799510</v>
       </c>
       <c r="B6" t="n">
-        <v>95953</v>
+        <v>90936</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312356</v>
+        <v>312300</v>
       </c>
       <c r="R6" t="n">
-        <v>6524442</v>
+        <v>6524200</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,6 +1199,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799503</v>
+        <v>122799505</v>
       </c>
       <c r="B7" t="n">
         <v>92233</v>
@@ -1260,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312342</v>
+        <v>312414</v>
       </c>
       <c r="R7" t="n">
-        <v>6524559</v>
+        <v>6524576</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799505</v>
+        <v>122799511</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>95953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,34 +1348,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312414</v>
+        <v>312263</v>
       </c>
       <c r="R8" t="n">
-        <v>6524576</v>
+        <v>6524163</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1377,17 +1387,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1408,6 +1418,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1424,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799497</v>
+        <v>122799509</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>91005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,39 +1465,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>5321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312066</v>
+        <v>312384</v>
       </c>
       <c r="R9" t="n">
-        <v>6524348</v>
+        <v>6524233</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,22 +1533,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1546,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799502</v>
+        <v>122799501</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,25 +1579,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,7 +1610,7 @@
         <v>312331</v>
       </c>
       <c r="R10" t="n">
-        <v>6524544</v>
+        <v>6524539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,6 +1653,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1765,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799510</v>
+        <v>122799497</v>
       </c>
       <c r="B12" t="n">
-        <v>90936</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,34 +1817,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4660</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312300</v>
+        <v>312066</v>
       </c>
       <c r="R12" t="n">
-        <v>6524200</v>
+        <v>6524348</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1854,17 +1895,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1882,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799507</v>
+        <v>122799502</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,25 +1935,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312377</v>
+        <v>312331</v>
       </c>
       <c r="R13" t="n">
-        <v>6524277</v>
+        <v>6524544</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,21 +2009,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1999,7 +2025,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799501</v>
+        <v>122799512</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2035,14 +2061,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312331</v>
+        <v>312193</v>
       </c>
       <c r="R14" t="n">
-        <v>6524539</v>
+        <v>6524137</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2054,17 +2080,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2116,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799515</v>
+        <v>122799496</v>
       </c>
       <c r="B15" t="n">
-        <v>92233</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,34 +2158,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312041</v>
+        <v>312061</v>
       </c>
       <c r="R15" t="n">
-        <v>6524041</v>
+        <v>6524311</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,17 +2202,17 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2202,6 +2233,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2218,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799511</v>
+        <v>122799498</v>
       </c>
       <c r="B16" t="n">
-        <v>95953</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,38 +2276,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312263</v>
+        <v>312152</v>
       </c>
       <c r="R16" t="n">
-        <v>6524163</v>
+        <v>6524347</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,17 +2319,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2307,17 +2353,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2335,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799498</v>
+        <v>122799508</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2375,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312152</v>
+        <v>312401</v>
       </c>
       <c r="R17" t="n">
-        <v>6524347</v>
+        <v>6524257</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2424,17 +2470,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2452,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799508</v>
+        <v>122799515</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,38 +2510,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312401</v>
+        <v>312041</v>
       </c>
       <c r="R18" t="n">
-        <v>6524257</v>
+        <v>6524041</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2507,17 +2553,17 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2538,21 +2584,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2569,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799509</v>
+        <v>122799513</v>
       </c>
       <c r="B19" t="n">
-        <v>91005</v>
+        <v>96898</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,21 +2616,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2609,10 +2640,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312384</v>
+        <v>312162</v>
       </c>
       <c r="R19" t="n">
-        <v>6524233</v>
+        <v>6524162</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,24 +2684,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2687,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799512</v>
+        <v>122799503</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,38 +2714,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312193</v>
+        <v>312342</v>
       </c>
       <c r="R20" t="n">
-        <v>6524137</v>
+        <v>6524559</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2742,17 +2757,17 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2773,21 +2788,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799507</v>
+        <v>122799512</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312377</v>
+        <v>312193</v>
       </c>
       <c r="R2" t="n">
-        <v>6524277</v>
+        <v>6524137</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799500</v>
+        <v>122799501</v>
       </c>
       <c r="B3" t="n">
-        <v>95953</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312356</v>
+        <v>312331</v>
       </c>
       <c r="R3" t="n">
-        <v>6524442</v>
+        <v>6524539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +878,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799506</v>
+        <v>122799509</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312417</v>
+        <v>312384</v>
       </c>
       <c r="R4" t="n">
-        <v>6524342</v>
+        <v>6524233</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,22 +993,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,7 +1027,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799499</v>
+        <v>122799505</v>
       </c>
       <c r="B5" t="n">
         <v>92233</v>
@@ -1051,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312153</v>
+        <v>312414</v>
       </c>
       <c r="R5" t="n">
-        <v>6524315</v>
+        <v>6524576</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799510</v>
+        <v>122799502</v>
       </c>
       <c r="B6" t="n">
-        <v>90936</v>
+        <v>92233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312300</v>
+        <v>312331</v>
       </c>
       <c r="R6" t="n">
-        <v>6524200</v>
+        <v>6524544</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,21 +1215,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799505</v>
+        <v>122799511</v>
       </c>
       <c r="B7" t="n">
-        <v>92233</v>
+        <v>95953</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,34 +1247,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312414</v>
+        <v>312263</v>
       </c>
       <c r="R7" t="n">
-        <v>6524576</v>
+        <v>6524163</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,17 +1286,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1316,6 +1317,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1332,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799511</v>
+        <v>122799515</v>
       </c>
       <c r="B8" t="n">
-        <v>95953</v>
+        <v>92233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312263</v>
+        <v>312041</v>
       </c>
       <c r="R8" t="n">
-        <v>6524163</v>
+        <v>6524041</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,21 +1434,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1449,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799509</v>
+        <v>122799497</v>
       </c>
       <c r="B9" t="n">
-        <v>91005</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,34 +1466,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5321</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312384</v>
+        <v>312066</v>
       </c>
       <c r="R9" t="n">
-        <v>6524233</v>
+        <v>6524348</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,23 +1539,22 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1567,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799501</v>
+        <v>122799496</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,38 +1584,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312331</v>
+        <v>312061</v>
       </c>
       <c r="R10" t="n">
-        <v>6524539</v>
+        <v>6524311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1656,17 +1666,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1684,7 +1694,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799504</v>
+        <v>122799498</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1724,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312390</v>
+        <v>312152</v>
       </c>
       <c r="R11" t="n">
-        <v>6524571</v>
+        <v>6524347</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1773,17 +1783,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1801,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799497</v>
+        <v>122799513</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>96898</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,39 +1827,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312066</v>
+        <v>312162</v>
       </c>
       <c r="R12" t="n">
-        <v>6524348</v>
+        <v>6524162</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,21 +1897,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1923,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799502</v>
+        <v>122799510</v>
       </c>
       <c r="B13" t="n">
-        <v>92233</v>
+        <v>90936</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1963,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312331</v>
+        <v>312300</v>
       </c>
       <c r="R13" t="n">
-        <v>6524544</v>
+        <v>6524200</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,6 +1999,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2025,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799512</v>
+        <v>122799503</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,38 +2042,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312193</v>
+        <v>312342</v>
       </c>
       <c r="R14" t="n">
-        <v>6524137</v>
+        <v>6524559</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2080,17 +2085,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2111,21 +2116,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2142,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799496</v>
+        <v>122799506</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,43 +2144,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312061</v>
+        <v>312417</v>
       </c>
       <c r="R15" t="n">
-        <v>6524311</v>
+        <v>6524342</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2236,17 +2221,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2264,7 +2249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799498</v>
+        <v>122799504</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2304,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312152</v>
+        <v>312390</v>
       </c>
       <c r="R16" t="n">
-        <v>6524347</v>
+        <v>6524571</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2353,17 +2338,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2381,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799508</v>
+        <v>122799499</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,25 +2378,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2421,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312401</v>
+        <v>312153</v>
       </c>
       <c r="R17" t="n">
-        <v>6524257</v>
+        <v>6524315</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2467,21 +2452,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2498,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799515</v>
+        <v>122799508</v>
       </c>
       <c r="B18" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,38 +2480,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312041</v>
+        <v>312401</v>
       </c>
       <c r="R18" t="n">
-        <v>6524041</v>
+        <v>6524257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2553,17 +2523,17 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2584,6 +2554,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2600,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799513</v>
+        <v>122799500</v>
       </c>
       <c r="B19" t="n">
-        <v>96898</v>
+        <v>95953</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,21 +2601,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2640,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312162</v>
+        <v>312356</v>
       </c>
       <c r="R19" t="n">
-        <v>6524162</v>
+        <v>6524442</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2702,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799503</v>
+        <v>122799507</v>
       </c>
       <c r="B20" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,25 +2699,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312342</v>
+        <v>312377</v>
       </c>
       <c r="R20" t="n">
-        <v>6524559</v>
+        <v>6524277</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2788,6 +2773,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799511</v>
+        <v>122799497</v>
       </c>
       <c r="B7" t="n">
-        <v>95953</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,34 +1247,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312263</v>
+        <v>312066</v>
       </c>
       <c r="R7" t="n">
-        <v>6524163</v>
+        <v>6524348</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,17 +1291,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1320,17 +1325,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1348,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799515</v>
+        <v>122799511</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>95953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312041</v>
+        <v>312263</v>
       </c>
       <c r="R8" t="n">
-        <v>6524041</v>
+        <v>6524163</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,6 +1439,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1450,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799497</v>
+        <v>122799515</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>92233</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,39 +1486,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312066</v>
+        <v>312041</v>
       </c>
       <c r="R9" t="n">
-        <v>6524348</v>
+        <v>6524041</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1510,17 +1525,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1541,21 +1556,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799496</v>
+        <v>122799498</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,43 +1584,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312061</v>
+        <v>312152</v>
       </c>
       <c r="R10" t="n">
-        <v>6524311</v>
+        <v>6524347</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1694,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799498</v>
+        <v>122799496</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,38 +1701,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312152</v>
+        <v>312061</v>
       </c>
       <c r="R11" t="n">
-        <v>6524347</v>
+        <v>6524311</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799498</v>
+        <v>122799496</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,38 +1584,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312152</v>
+        <v>312061</v>
       </c>
       <c r="R10" t="n">
-        <v>6524347</v>
+        <v>6524311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799496</v>
+        <v>122799498</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,43 +1706,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312061</v>
+        <v>312152</v>
       </c>
       <c r="R11" t="n">
-        <v>6524311</v>
+        <v>6524347</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799512</v>
+        <v>122799502</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>92236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312193</v>
+        <v>312331</v>
       </c>
       <c r="R2" t="n">
-        <v>6524137</v>
+        <v>6524544</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799501</v>
+        <v>122799509</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312331</v>
+        <v>312384</v>
       </c>
       <c r="R3" t="n">
-        <v>6524539</v>
+        <v>6524233</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,22 +861,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799509</v>
+        <v>122799506</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312384</v>
+        <v>312417</v>
       </c>
       <c r="R4" t="n">
-        <v>6524233</v>
+        <v>6524342</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,23 +979,22 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1027,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799505</v>
+        <v>122799510</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>90939</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312414</v>
+        <v>312300</v>
       </c>
       <c r="R5" t="n">
-        <v>6524576</v>
+        <v>6524200</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,6 +1098,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799502</v>
+        <v>122799512</v>
       </c>
       <c r="B6" t="n">
-        <v>92233</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,38 +1141,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312331</v>
+        <v>312193</v>
       </c>
       <c r="R6" t="n">
-        <v>6524544</v>
+        <v>6524137</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1215,6 +1215,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1231,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799497</v>
+        <v>122799496</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312066</v>
+        <v>312061</v>
       </c>
       <c r="R7" t="n">
-        <v>6524348</v>
+        <v>6524311</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799511</v>
+        <v>122799513</v>
       </c>
       <c r="B8" t="n">
-        <v>95953</v>
+        <v>96901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,34 +1384,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312263</v>
+        <v>312162</v>
       </c>
       <c r="R8" t="n">
-        <v>6524163</v>
+        <v>6524162</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1408,17 +1423,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1439,21 +1454,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,7 +1473,7 @@
         <v>122799515</v>
       </c>
       <c r="B9" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799498</v>
+        <v>122799499</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>92236</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312152</v>
+        <v>312153</v>
       </c>
       <c r="R10" t="n">
-        <v>6524347</v>
+        <v>6524315</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,21 +1658,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1689,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799496</v>
+        <v>122799511</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>95956</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,39 +1690,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312061</v>
+        <v>312263</v>
       </c>
       <c r="R11" t="n">
-        <v>6524311</v>
+        <v>6524163</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,17 +1729,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1783,17 +1763,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1811,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799513</v>
+        <v>122799508</v>
       </c>
       <c r="B12" t="n">
-        <v>96898</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,25 +1803,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1831,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312162</v>
+        <v>312401</v>
       </c>
       <c r="R12" t="n">
-        <v>6524162</v>
+        <v>6524257</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1897,6 +1877,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1913,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799510</v>
+        <v>122799503</v>
       </c>
       <c r="B13" t="n">
-        <v>90936</v>
+        <v>92236</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1924,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312300</v>
+        <v>312342</v>
       </c>
       <c r="R13" t="n">
-        <v>6524200</v>
+        <v>6524559</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1999,21 +1994,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2030,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799503</v>
+        <v>122799505</v>
       </c>
       <c r="B14" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312342</v>
+        <v>312414</v>
       </c>
       <c r="R14" t="n">
-        <v>6524559</v>
+        <v>6524576</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2132,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799506</v>
+        <v>122799500</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>95956</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,25 +2124,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312417</v>
+        <v>312356</v>
       </c>
       <c r="R15" t="n">
-        <v>6524342</v>
+        <v>6524442</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2218,21 +2198,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2249,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799504</v>
+        <v>122799498</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312390</v>
+        <v>312152</v>
       </c>
       <c r="R16" t="n">
-        <v>6524571</v>
+        <v>6524347</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2338,17 +2303,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2366,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799499</v>
+        <v>122799504</v>
       </c>
       <c r="B17" t="n">
-        <v>92233</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,25 +2343,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312153</v>
+        <v>312390</v>
       </c>
       <c r="R17" t="n">
-        <v>6524315</v>
+        <v>6524571</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,6 +2417,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2468,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799508</v>
+        <v>122799507</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312401</v>
+        <v>312377</v>
       </c>
       <c r="R18" t="n">
-        <v>6524257</v>
+        <v>6524277</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2585,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799500</v>
+        <v>122799501</v>
       </c>
       <c r="B19" t="n">
-        <v>95953</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2597,25 +2577,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2605,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312356</v>
+        <v>312331</v>
       </c>
       <c r="R19" t="n">
-        <v>6524442</v>
+        <v>6524539</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2671,6 +2651,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2687,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799507</v>
+        <v>122799497</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,38 +2694,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312377</v>
+        <v>312066</v>
       </c>
       <c r="R20" t="n">
-        <v>6524277</v>
+        <v>6524348</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799502</v>
+        <v>122799508</v>
       </c>
       <c r="B2" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312331</v>
+        <v>312401</v>
       </c>
       <c r="R2" t="n">
-        <v>6524544</v>
+        <v>6524257</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799509</v>
+        <v>122799513</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>96903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312384</v>
+        <v>312162</v>
       </c>
       <c r="R3" t="n">
-        <v>6524233</v>
+        <v>6524162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,24 +876,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799506</v>
+        <v>122799511</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>95958</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,38 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312417</v>
+        <v>312263</v>
       </c>
       <c r="R4" t="n">
-        <v>6524342</v>
+        <v>6524163</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -950,17 +949,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1012,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799510</v>
+        <v>122799509</v>
       </c>
       <c r="B5" t="n">
-        <v>90939</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312300</v>
+        <v>312384</v>
       </c>
       <c r="R5" t="n">
-        <v>6524200</v>
+        <v>6524233</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,6 +1095,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799512</v>
+        <v>122799499</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,38 +1141,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312193</v>
+        <v>312153</v>
       </c>
       <c r="R6" t="n">
-        <v>6524137</v>
+        <v>6524315</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1215,21 +1215,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1246,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799496</v>
+        <v>122799500</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>95958</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,39 +1247,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312061</v>
+        <v>312356</v>
       </c>
       <c r="R7" t="n">
-        <v>6524311</v>
+        <v>6524442</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,21 +1317,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1368,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799513</v>
+        <v>122799498</v>
       </c>
       <c r="B8" t="n">
-        <v>96901</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312162</v>
+        <v>312152</v>
       </c>
       <c r="R8" t="n">
-        <v>6524162</v>
+        <v>6524347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,6 +1419,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1470,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799515</v>
+        <v>122799507</v>
       </c>
       <c r="B9" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,38 +1462,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312041</v>
+        <v>312377</v>
       </c>
       <c r="R9" t="n">
-        <v>6524041</v>
+        <v>6524277</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,17 +1505,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1556,6 +1536,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1572,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799499</v>
+        <v>122799510</v>
       </c>
       <c r="B10" t="n">
-        <v>92236</v>
+        <v>90941</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,21 +1583,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312153</v>
+        <v>312300</v>
       </c>
       <c r="R10" t="n">
-        <v>6524315</v>
+        <v>6524200</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,6 +1653,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1674,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799511</v>
+        <v>122799501</v>
       </c>
       <c r="B11" t="n">
-        <v>95956</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,38 +1696,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312263</v>
+        <v>312331</v>
       </c>
       <c r="R11" t="n">
-        <v>6524163</v>
+        <v>6524539</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1729,17 +1739,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1791,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799508</v>
+        <v>122799496</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,38 +1813,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312401</v>
+        <v>312061</v>
       </c>
       <c r="R12" t="n">
-        <v>6524257</v>
+        <v>6524311</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1880,17 +1895,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1908,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799503</v>
+        <v>122799512</v>
       </c>
       <c r="B13" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,38 +1935,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312342</v>
+        <v>312193</v>
       </c>
       <c r="R13" t="n">
-        <v>6524559</v>
+        <v>6524137</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,17 +1978,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1994,6 +2009,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2010,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799505</v>
+        <v>122799503</v>
       </c>
       <c r="B14" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312414</v>
+        <v>312342</v>
       </c>
       <c r="R14" t="n">
-        <v>6524576</v>
+        <v>6524559</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2112,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799500</v>
+        <v>122799505</v>
       </c>
       <c r="B15" t="n">
-        <v>95956</v>
+        <v>92238</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,21 +2158,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312356</v>
+        <v>312414</v>
       </c>
       <c r="R15" t="n">
-        <v>6524442</v>
+        <v>6524576</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2214,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799498</v>
+        <v>122799515</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,38 +2256,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312152</v>
+        <v>312041</v>
       </c>
       <c r="R16" t="n">
-        <v>6524347</v>
+        <v>6524041</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2269,17 +2299,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2300,21 +2330,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2331,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799504</v>
+        <v>122799497</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,38 +2358,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312390</v>
+        <v>312066</v>
       </c>
       <c r="R17" t="n">
-        <v>6524571</v>
+        <v>6524348</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2420,17 +2440,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2448,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799507</v>
+        <v>122799502</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,25 +2480,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2488,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312377</v>
+        <v>312331</v>
       </c>
       <c r="R18" t="n">
-        <v>6524277</v>
+        <v>6524544</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2534,21 +2554,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2565,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799501</v>
+        <v>122799506</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312331</v>
+        <v>312417</v>
       </c>
       <c r="R19" t="n">
-        <v>6524539</v>
+        <v>6524342</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2682,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799497</v>
+        <v>122799504</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2694,43 +2699,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312066</v>
+        <v>312390</v>
       </c>
       <c r="R20" t="n">
-        <v>6524348</v>
+        <v>6524571</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799508</v>
+        <v>122799509</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>91016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312401</v>
+        <v>312384</v>
       </c>
       <c r="R2" t="n">
-        <v>6524257</v>
+        <v>6524233</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,22 +759,23 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799513</v>
+        <v>122799500</v>
       </c>
       <c r="B3" t="n">
-        <v>96903</v>
+        <v>95964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312162</v>
+        <v>312356</v>
       </c>
       <c r="R3" t="n">
-        <v>6524162</v>
+        <v>6524442</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799511</v>
+        <v>122799496</v>
       </c>
       <c r="B4" t="n">
-        <v>95958</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,34 +911,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312263</v>
+        <v>312061</v>
       </c>
       <c r="R4" t="n">
-        <v>6524163</v>
+        <v>6524311</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,17 +955,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -983,17 +989,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799509</v>
+        <v>122799510</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>90947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312384</v>
+        <v>312300</v>
       </c>
       <c r="R5" t="n">
-        <v>6524233</v>
+        <v>6524200</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1101,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799499</v>
+        <v>122799508</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,25 +1146,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312153</v>
+        <v>312401</v>
       </c>
       <c r="R6" t="n">
-        <v>6524315</v>
+        <v>6524257</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,6 +1220,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1231,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799500</v>
+        <v>122799512</v>
       </c>
       <c r="B7" t="n">
-        <v>95958</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,38 +1263,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312356</v>
+        <v>312193</v>
       </c>
       <c r="R7" t="n">
-        <v>6524442</v>
+        <v>6524137</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,17 +1306,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1317,6 +1337,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1333,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799498</v>
+        <v>122799515</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>92244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,38 +1380,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312152</v>
+        <v>312041</v>
       </c>
       <c r="R8" t="n">
-        <v>6524347</v>
+        <v>6524041</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,17 +1423,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1419,21 +1454,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1450,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799507</v>
+        <v>122799511</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>95964</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,38 +1482,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312377</v>
+        <v>312263</v>
       </c>
       <c r="R9" t="n">
-        <v>6524277</v>
+        <v>6524163</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,17 +1525,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1567,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799510</v>
+        <v>122799503</v>
       </c>
       <c r="B10" t="n">
-        <v>90941</v>
+        <v>92244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,21 +1603,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312300</v>
+        <v>312342</v>
       </c>
       <c r="R10" t="n">
-        <v>6524200</v>
+        <v>6524559</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,21 +1673,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1684,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799501</v>
+        <v>122799502</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>92244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,25 +1701,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,7 +1732,7 @@
         <v>312331</v>
       </c>
       <c r="R11" t="n">
-        <v>6524539</v>
+        <v>6524544</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,21 +1775,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1801,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799496</v>
+        <v>122799499</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>92244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,39 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312061</v>
+        <v>312153</v>
       </c>
       <c r="R12" t="n">
-        <v>6524311</v>
+        <v>6524315</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,21 +1877,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1923,10 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799512</v>
+        <v>122799504</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,14 +1929,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312193</v>
+        <v>312390</v>
       </c>
       <c r="R13" t="n">
-        <v>6524137</v>
+        <v>6524571</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1978,17 +1948,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2040,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799503</v>
+        <v>122799513</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>96909</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,21 +2026,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312342</v>
+        <v>312162</v>
       </c>
       <c r="R14" t="n">
-        <v>6524559</v>
+        <v>6524162</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2142,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799505</v>
+        <v>122799498</v>
       </c>
       <c r="B15" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,25 +2124,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312414</v>
+        <v>312152</v>
       </c>
       <c r="R15" t="n">
-        <v>6524576</v>
+        <v>6524347</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,6 +2198,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2244,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799515</v>
+        <v>122799507</v>
       </c>
       <c r="B16" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,38 +2241,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312041</v>
+        <v>312377</v>
       </c>
       <c r="R16" t="n">
-        <v>6524041</v>
+        <v>6524277</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,17 +2284,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2330,6 +2315,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799497</v>
+        <v>122799501</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,43 +2358,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312066</v>
+        <v>312331</v>
       </c>
       <c r="R17" t="n">
-        <v>6524348</v>
+        <v>6524539</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2440,17 +2435,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799502</v>
+        <v>122799506</v>
       </c>
       <c r="B18" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,25 +2475,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2508,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312331</v>
+        <v>312417</v>
       </c>
       <c r="R18" t="n">
-        <v>6524544</v>
+        <v>6524342</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,6 +2549,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2570,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799506</v>
+        <v>122799505</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>92244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,25 +2592,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312417</v>
+        <v>312414</v>
       </c>
       <c r="R19" t="n">
-        <v>6524342</v>
+        <v>6524576</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2656,21 +2666,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2687,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799504</v>
+        <v>122799497</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,38 +2694,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312390</v>
+        <v>312066</v>
       </c>
       <c r="R20" t="n">
-        <v>6524571</v>
+        <v>6524348</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799509</v>
+        <v>122799511</v>
       </c>
       <c r="B2" t="n">
-        <v>91016</v>
+        <v>95967</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312384</v>
+        <v>312263</v>
       </c>
       <c r="R2" t="n">
-        <v>6524233</v>
+        <v>6524163</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,23 +759,22 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -793,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799500</v>
+        <v>122799510</v>
       </c>
       <c r="B3" t="n">
-        <v>95964</v>
+        <v>90950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312356</v>
+        <v>312300</v>
       </c>
       <c r="R3" t="n">
-        <v>6524442</v>
+        <v>6524200</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +878,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799496</v>
+        <v>122799513</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>96912</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312061</v>
+        <v>312162</v>
       </c>
       <c r="R4" t="n">
-        <v>6524311</v>
+        <v>6524162</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,21 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1017,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799510</v>
+        <v>122799508</v>
       </c>
       <c r="B5" t="n">
-        <v>90947</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312300</v>
+        <v>312401</v>
       </c>
       <c r="R5" t="n">
-        <v>6524200</v>
+        <v>6524257</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,17 +1100,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1134,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799508</v>
+        <v>122799498</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312401</v>
+        <v>312152</v>
       </c>
       <c r="R6" t="n">
-        <v>6524257</v>
+        <v>6524347</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,17 +1217,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1251,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799512</v>
+        <v>122799500</v>
       </c>
       <c r="B7" t="n">
-        <v>78772</v>
+        <v>95967</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,38 +1257,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312193</v>
+        <v>312356</v>
       </c>
       <c r="R7" t="n">
-        <v>6524137</v>
+        <v>6524442</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1306,17 +1300,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1337,21 +1331,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1368,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799515</v>
+        <v>122799497</v>
       </c>
       <c r="B8" t="n">
-        <v>92244</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,34 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312041</v>
+        <v>312066</v>
       </c>
       <c r="R8" t="n">
-        <v>6524041</v>
+        <v>6524348</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,17 +1407,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1454,6 +1438,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1470,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799511</v>
+        <v>122799506</v>
       </c>
       <c r="B9" t="n">
-        <v>95964</v>
+        <v>78775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,38 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312263</v>
+        <v>312417</v>
       </c>
       <c r="R9" t="n">
-        <v>6524163</v>
+        <v>6524342</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,17 +1524,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1587,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799503</v>
+        <v>122799509</v>
       </c>
       <c r="B10" t="n">
-        <v>92244</v>
+        <v>91019</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1627,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312342</v>
+        <v>312384</v>
       </c>
       <c r="R10" t="n">
-        <v>6524559</v>
+        <v>6524233</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1671,8 +1670,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1689,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799502</v>
+        <v>122799501</v>
       </c>
       <c r="B11" t="n">
-        <v>92244</v>
+        <v>78775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,25 +1716,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,7 +1747,7 @@
         <v>312331</v>
       </c>
       <c r="R11" t="n">
-        <v>6524544</v>
+        <v>6524539</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,6 +1790,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1791,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799499</v>
+        <v>122799505</v>
       </c>
       <c r="B12" t="n">
-        <v>92244</v>
+        <v>92247</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312153</v>
+        <v>312414</v>
       </c>
       <c r="R12" t="n">
-        <v>6524315</v>
+        <v>6524576</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1893,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799504</v>
+        <v>122799496</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,38 +1935,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312390</v>
+        <v>312061</v>
       </c>
       <c r="R13" t="n">
-        <v>6524571</v>
+        <v>6524311</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,17 +2017,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2010,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799513</v>
+        <v>122799503</v>
       </c>
       <c r="B14" t="n">
-        <v>96909</v>
+        <v>92247</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,21 +2061,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2050,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312162</v>
+        <v>312342</v>
       </c>
       <c r="R14" t="n">
-        <v>6524162</v>
+        <v>6524559</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2112,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122799498</v>
+        <v>122799504</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>312152</v>
+        <v>312390</v>
       </c>
       <c r="R15" t="n">
-        <v>6524347</v>
+        <v>6524571</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2201,17 +2236,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2229,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799507</v>
+        <v>122799515</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>92247</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,38 +2276,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312377</v>
+        <v>312041</v>
       </c>
       <c r="R16" t="n">
-        <v>6524277</v>
+        <v>6524041</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2284,17 +2319,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2315,21 +2350,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2346,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799501</v>
+        <v>122799502</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>92247</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,25 +2378,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,7 +2409,7 @@
         <v>312331</v>
       </c>
       <c r="R17" t="n">
-        <v>6524539</v>
+        <v>6524544</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,21 +2452,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2463,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799506</v>
+        <v>122799507</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312417</v>
+        <v>312377</v>
       </c>
       <c r="R18" t="n">
-        <v>6524342</v>
+        <v>6524277</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2580,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122799505</v>
+        <v>122799512</v>
       </c>
       <c r="B19" t="n">
-        <v>92244</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,38 +2597,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312414</v>
+        <v>312193</v>
       </c>
       <c r="R19" t="n">
-        <v>6524576</v>
+        <v>6524137</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2635,17 +2640,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2666,6 +2671,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2682,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799497</v>
+        <v>122799499</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>92247</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,39 +2718,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312066</v>
+        <v>312153</v>
       </c>
       <c r="R20" t="n">
-        <v>6524348</v>
+        <v>6524315</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2773,21 +2788,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +2802,875 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125553319</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Keddebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>312214</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6524199</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På stammen av gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125553888</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Krddebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>312186</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6524178</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125553915</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Munkedsal Krddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>312220</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6524149</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två garnlavar som snurrat ohop</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125552952</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>312368</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6524545</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125552766</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dals Ed Töftrdal Keddebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>312259</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6524320</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera gnagspår på barklöd tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125544216</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95942</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Keddebo Dals Ed, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>312339</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6524459</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125553679</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Keddebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>312173</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6524171</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ett större nystan</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125553938</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Krddebo Dals Ed, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>312222</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6524274</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2807,7 +2807,7 @@
         <v>125553319</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>125553888</v>
       </c>
       <c r="B22" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>125553915</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>125552952</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>125544216</v>
       </c>
       <c r="B26" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>125553679</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>125553938</v>
       </c>
       <c r="B28" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553319</v>
+        <v>125553888</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,41 +2815,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312214</v>
+        <v>312186</v>
       </c>
       <c r="R21" t="n">
-        <v>6524199</v>
+        <v>6524178</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2886,7 +2883,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,14 +2892,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2919,10 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553888</v>
+        <v>125553319</v>
       </c>
       <c r="B22" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,38 +2921,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312186</v>
+        <v>312214</v>
       </c>
       <c r="R22" t="n">
-        <v>6524178</v>
+        <v>6524199</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,8 +3001,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3355,7 +3355,7 @@
         <v>125544216</v>
       </c>
       <c r="B26" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>125544216</v>
       </c>
       <c r="B26" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553888</v>
+        <v>125553319</v>
       </c>
       <c r="B21" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,38 +2815,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312186</v>
+        <v>312214</v>
       </c>
       <c r="R21" t="n">
-        <v>6524178</v>
+        <v>6524199</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2883,7 +2886,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,8 +2895,14 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2910,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553319</v>
+        <v>125553888</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,41 +2930,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312214</v>
+        <v>312186</v>
       </c>
       <c r="R22" t="n">
-        <v>6524199</v>
+        <v>6524178</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2992,7 +2998,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,14 +3007,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2807,7 +2807,7 @@
         <v>125553319</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>125553888</v>
       </c>
       <c r="B22" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>125553915</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>125552952</v>
       </c>
       <c r="B24" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>125544216</v>
       </c>
       <c r="B26" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>125553679</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>125553938</v>
       </c>
       <c r="B28" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>125544216</v>
       </c>
       <c r="B26" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553319</v>
+        <v>125553888</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,41 +2815,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312214</v>
+        <v>312186</v>
       </c>
       <c r="R21" t="n">
-        <v>6524199</v>
+        <v>6524178</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2886,7 +2883,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,14 +2892,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2919,10 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553888</v>
+        <v>125553319</v>
       </c>
       <c r="B22" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,38 +2921,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312186</v>
+        <v>312214</v>
       </c>
       <c r="R22" t="n">
-        <v>6524178</v>
+        <v>6524199</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,8 +3001,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3025,10 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125553915</v>
+        <v>125552952</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,37 +3036,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Munkedsal Krddebo, Boh</t>
+          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>312220</v>
+        <v>312368</v>
       </c>
       <c r="R23" t="n">
-        <v>6524149</v>
+        <v>6524545</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3078,17 +3087,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3101,18 +3110,12 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två garnlavar som snurrat ohop</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3131,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125552952</v>
+        <v>125553915</v>
       </c>
       <c r="B24" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,46 +3145,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
+          <t>Munkedsal Krddebo, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312368</v>
+        <v>312220</v>
       </c>
       <c r="R24" t="n">
-        <v>6524545</v>
+        <v>6524149</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3193,17 +3187,17 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3216,12 +3210,18 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Två garnlavar som snurrat ohop</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553888</v>
+        <v>125553319</v>
       </c>
       <c r="B21" t="n">
-        <v>57653</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,38 +2815,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312186</v>
+        <v>312214</v>
       </c>
       <c r="R21" t="n">
-        <v>6524178</v>
+        <v>6524199</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2883,7 +2886,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,8 +2895,14 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2910,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553319</v>
+        <v>125553888</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,41 +2930,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312214</v>
+        <v>312186</v>
       </c>
       <c r="R22" t="n">
-        <v>6524199</v>
+        <v>6524178</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2992,7 +2998,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,14 +3007,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3025,10 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125552952</v>
+        <v>125553915</v>
       </c>
       <c r="B23" t="n">
-        <v>57653</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,46 +3036,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
+          <t>Munkedsal Krddebo, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>312368</v>
+        <v>312220</v>
       </c>
       <c r="R23" t="n">
-        <v>6524545</v>
+        <v>6524149</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3087,17 +3078,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3110,12 +3101,18 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två garnlavar som snurrat ohop</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3134,10 +3131,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125553915</v>
+        <v>125552952</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,37 +3142,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Munkedsal Krddebo, Boh</t>
+          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312220</v>
+        <v>312368</v>
       </c>
       <c r="R24" t="n">
-        <v>6524149</v>
+        <v>6524545</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3187,17 +3193,17 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3210,18 +3216,12 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Två garnlavar som snurrat ohop</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>125544216</v>
       </c>
       <c r="B26" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>125553679</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>125553938</v>
       </c>
       <c r="B28" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553319</v>
+        <v>125553888</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,41 +2815,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312214</v>
+        <v>312186</v>
       </c>
       <c r="R21" t="n">
-        <v>6524199</v>
+        <v>6524178</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2886,7 +2883,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,14 +2892,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2919,10 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553888</v>
+        <v>125553319</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,38 +2921,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312186</v>
+        <v>312214</v>
       </c>
       <c r="R22" t="n">
-        <v>6524178</v>
+        <v>6524199</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2998,7 +2992,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,8 +3001,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -2804,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553888</v>
+        <v>125553319</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,38 +2815,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312186</v>
+        <v>312214</v>
       </c>
       <c r="R21" t="n">
-        <v>6524178</v>
+        <v>6524199</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2883,7 +2886,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,8 +2895,14 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2910,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553319</v>
+        <v>125553888</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,41 +2930,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312214</v>
+        <v>312186</v>
       </c>
       <c r="R22" t="n">
-        <v>6524199</v>
+        <v>6524178</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2992,7 +2998,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,14 +3007,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122799511</v>
+        <v>125544216</v>
       </c>
       <c r="B2" t="n">
-        <v>95967</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Keddebo Dals Ed, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>312263</v>
+        <v>312339</v>
       </c>
       <c r="R2" t="n">
-        <v>6524163</v>
+        <v>6524459</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -730,27 +733,27 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,48 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122799510</v>
+        <v>122799513</v>
       </c>
       <c r="B3" t="n">
-        <v>90950</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>312300</v>
+        <v>312162</v>
       </c>
       <c r="R3" t="n">
-        <v>6524200</v>
+        <v>6524162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,21 +862,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122799513</v>
+        <v>122799500</v>
       </c>
       <c r="B4" t="n">
-        <v>96912</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>312162</v>
+        <v>312356</v>
       </c>
       <c r="R4" t="n">
-        <v>6524162</v>
+        <v>6524442</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,50 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122799508</v>
+        <v>122799511</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312401</v>
+        <v>312263</v>
       </c>
       <c r="R5" t="n">
-        <v>6524257</v>
+        <v>6524163</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,17 +1025,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1128,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122799498</v>
+        <v>122799499</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312152</v>
+        <v>312153</v>
       </c>
       <c r="R6" t="n">
-        <v>6524347</v>
+        <v>6524315</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,21 +1168,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1245,37 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122799500</v>
+        <v>122799502</v>
       </c>
       <c r="B7" t="n">
-        <v>95967</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>312356</v>
+        <v>312331</v>
       </c>
       <c r="R7" t="n">
-        <v>6524442</v>
+        <v>6524544</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1347,55 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122799497</v>
+        <v>122799503</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>312066</v>
+        <v>312342</v>
       </c>
       <c r="R8" t="n">
-        <v>6524348</v>
+        <v>6524559</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,21 +1362,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1469,15 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122799506</v>
+        <v>122799505</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>312417</v>
+        <v>312414</v>
       </c>
       <c r="R9" t="n">
-        <v>6524342</v>
+        <v>6524576</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,21 +1459,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1586,50 +1475,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122799509</v>
+        <v>122799515</v>
       </c>
       <c r="B10" t="n">
-        <v>91019</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5321</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Skog norr om Korpetjärnet, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312384</v>
+        <v>312041</v>
       </c>
       <c r="R10" t="n">
-        <v>6524233</v>
+        <v>6524041</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,17 +1525,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1670,24 +1554,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1704,37 +1572,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122799501</v>
+        <v>122799510</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1744,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312331</v>
+        <v>312300</v>
       </c>
       <c r="R11" t="n">
-        <v>6524539</v>
+        <v>6524200</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1793,17 +1656,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1821,15 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122799496</v>
+        <v>122799509</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,39 +1695,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>5321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312061</v>
+        <v>312384</v>
       </c>
       <c r="R12" t="n">
-        <v>6524311</v>
+        <v>6524233</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1910,22 +1763,23 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1943,37 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122799505</v>
+        <v>122799498</v>
       </c>
       <c r="B13" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1983,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312414</v>
+        <v>312152</v>
       </c>
       <c r="R13" t="n">
-        <v>6524576</v>
+        <v>6524347</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2029,6 +1878,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2045,37 +1909,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122799503</v>
+        <v>122799501</v>
       </c>
       <c r="B14" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312342</v>
+        <v>312331</v>
       </c>
       <c r="R14" t="n">
-        <v>6524559</v>
+        <v>6524539</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2131,6 +1990,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2150,16 +2024,11 @@
         <v>122799504</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2264,50 +2133,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122799515</v>
+        <v>122799506</v>
       </c>
       <c r="B16" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Boh</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>312041</v>
+        <v>312417</v>
       </c>
       <c r="R16" t="n">
-        <v>6524041</v>
+        <v>6524342</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,17 +2183,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2350,6 +2214,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2366,37 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122799502</v>
+        <v>122799507</v>
       </c>
       <c r="B17" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312331</v>
+        <v>312377</v>
       </c>
       <c r="R17" t="n">
-        <v>6524544</v>
+        <v>6524277</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,6 +2326,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2468,19 +2357,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122799507</v>
+        <v>122799508</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2508,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312377</v>
+        <v>312401</v>
       </c>
       <c r="R18" t="n">
-        <v>6524277</v>
+        <v>6524257</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2588,16 +2472,11 @@
         <v>122799512</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2702,53 +2581,55 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122799499</v>
+        <v>125553319</v>
       </c>
       <c r="B20" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog norr om Korpetjärnet, Dls</t>
+          <t>Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312153</v>
+        <v>312214</v>
       </c>
       <c r="R20" t="n">
-        <v>6524315</v>
+        <v>6524199</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,12 +2653,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stammen av gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,32 +2672,38 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125553319</v>
+        <v>125553679</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2846,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312214</v>
+        <v>312173</v>
       </c>
       <c r="R21" t="n">
-        <v>6524199</v>
+        <v>6524171</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2886,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På stammen av gran</t>
+          <t>Ett större nystan</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,11 +2790,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2919,49 +2806,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125553888</v>
+        <v>125553915</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krddebo, Dls</t>
+          <t>Munkedsal Krddebo, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>312186</v>
+        <v>312220</v>
       </c>
       <c r="R22" t="n">
-        <v>6524178</v>
+        <v>6524149</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2973,17 +2859,17 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Dals-Ed</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Töftedal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2998,7 +2884,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
+          <t>Två garnlavar som snurrat ohop</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,6 +2893,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3025,48 +2912,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125553915</v>
+        <v>125552869</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Munkedsal Krddebo, Boh</t>
+          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>312220</v>
+        <v>312368</v>
       </c>
       <c r="R23" t="n">
-        <v>6524149</v>
+        <v>6524545</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3078,17 +2966,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Munkedal</t>
+          <t>Dals-Ed</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Bohuslän</t>
+          <t>Dalsland</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Krokstad</t>
+          <t>Töftedal</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3103,7 +2991,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Två garnlavar som snurrat ohop</t>
+          <t>Äldre havk</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,9 +3000,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3131,14 +3023,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125552952</v>
+        <v>125553888</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3159,29 +3051,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Krddebo, Töftedal, Dals Ed, Dls</t>
+          <t>Krddebo, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312368</v>
+        <v>312186</v>
       </c>
       <c r="R24" t="n">
-        <v>6524545</v>
+        <v>6524178</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,6 +3098,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hack vid basen av rn gran som tyvktes levande</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125552766</v>
+        <v>125553938</v>
       </c>
       <c r="B25" t="n">
-        <v>5176</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,43 +3140,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dals Ed Töftrdal Keddebo, Dls</t>
+          <t>Krddebo Dals Ed, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312259</v>
+        <v>312222</v>
       </c>
       <c r="R25" t="n">
-        <v>6524320</v>
+        <v>6524274</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3322,18 +3210,12 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera gnagspår på barklöd tall</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125544216</v>
+        <v>122799497</v>
       </c>
       <c r="B26" t="n">
-        <v>95964</v>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,45 +3245,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Keddebo Dals Ed, Dls</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312339</v>
+        <v>312066</v>
       </c>
       <c r="R26" t="n">
-        <v>6524459</v>
+        <v>6524348</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,12 +3304,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,71 +3318,87 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125553679</v>
+        <v>125552766</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Keddebo, Dls</t>
+          <t>Dals Ed Töftrdal Keddebo, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>312173</v>
+        <v>312259</v>
       </c>
       <c r="R27" t="n">
-        <v>6524171</v>
+        <v>6524320</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3540,7 +3435,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ett större nystan</t>
+          <t>Flera gnagspår på barklöd tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,27 +3463,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125553938</v>
+        <v>122799496</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>5199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3597,27 +3492,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Krddebo Dals Ed, Dls</t>
+          <t>Skog norr om Korpetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>312222</v>
+        <v>312061</v>
       </c>
       <c r="R28" t="n">
-        <v>6524274</v>
+        <v>6524311</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3641,12 +3533,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3657,16 +3549,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 60410-2024 artfynd.xlsx
+++ b/artfynd/A 60410-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125544216</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799513</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799499</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799503</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799505</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799515</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799510</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799509</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799498</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799501</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799504</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799506</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799507</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2466,6 +2551,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799508</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799512</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2693,6 +2788,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125553319</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125553679</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125553915</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3020,6 +3130,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125552869</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3126,6 +3241,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125553888</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3231,6 +3351,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125553938</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3348,6 +3473,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799497</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3460,6 +3590,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125552766</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3577,8 +3712,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122799496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>